--- a/uploads/licence_report.xlsx
+++ b/uploads/licence_report.xlsx
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="8" customHeight="1">
